--- a/app/data/raw/students/ETUDIANTS_M1_RIB_G11_S1.xlsx
+++ b/app/data/raw/students/ETUDIANTS_M1_RIB_G11_S1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Automa départ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4A6504-74DF-4DE5-A979-A679658F1C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DFE512-3876-45BD-B08F-09688584A993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="69">
   <si>
     <t>Annee</t>
   </si>
@@ -205,13 +205,40 @@
   </si>
   <si>
     <t>G11</t>
+  </si>
+  <si>
+    <t>ACHOUI</t>
+  </si>
+  <si>
+    <t>AHMED FARES</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>BOUGHEFALA</t>
+  </si>
+  <si>
+    <t>MOHAMED AMINE</t>
+  </si>
+  <si>
+    <t>GHEMBAZA</t>
+  </si>
+  <si>
+    <t>ZAHIA</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,6 +250,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -606,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -690,10 +723,10 @@
         <v>59</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -716,10 +749,10 @@
         <v>59</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L4" t="s">
         <v>47</v>
@@ -742,10 +775,10 @@
         <v>59</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L5" t="s">
         <v>48</v>
@@ -768,10 +801,10 @@
         <v>59</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L6" t="s">
         <v>49</v>
@@ -794,10 +827,10 @@
         <v>59</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L7" t="s">
         <v>50</v>
@@ -820,10 +853,10 @@
         <v>59</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L8" t="s">
         <v>51</v>
@@ -846,10 +879,10 @@
         <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="H9" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="L9" t="s">
         <v>52</v>
@@ -872,10 +905,10 @@
         <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L10" t="s">
         <v>53</v>
@@ -898,10 +931,10 @@
         <v>59</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="H11" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="L11" t="s">
         <v>54</v>
@@ -924,10 +957,10 @@
         <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L12" t="s">
         <v>55</v>
@@ -950,13 +983,10 @@
         <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="L13" t="s">
         <v>56</v>
@@ -979,10 +1009,10 @@
         <v>59</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L14" t="s">
         <v>57</v>
@@ -1005,16 +1035,98 @@
         <v>59</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L15" t="s">
         <v>58</v>
       </c>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" t="s">
+        <v>41</v>
+      </c>
+      <c r="K16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" t="s">
+        <v>42</v>
+      </c>
+      <c r="L17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>